--- a/TestData/TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
+++ b/TestData/TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2CE22A-76C3-4A95-93F6-C3807B54E03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFAAE03-97C2-4C31-B281-C76D9A64750D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="AddContact" sheetId="3" r:id="rId3"/>
-    <sheet name="AssociatedOpp" sheetId="4" r:id="rId4"/>
-    <sheet name="AssociatedEng" sheetId="5" r:id="rId5"/>
+    <sheet name="AppName" sheetId="6" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="7" r:id="rId3"/>
+    <sheet name="Users" sheetId="2" r:id="rId4"/>
+    <sheet name="AddContact" sheetId="3" r:id="rId5"/>
+    <sheet name="AssociatedOpp" sheetId="4" r:id="rId6"/>
+    <sheet name="AssociatedEng" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="82">
   <si>
     <t>Client</t>
   </si>
@@ -229,15 +231,9 @@
     <t>Ayati Arvind</t>
   </si>
   <si>
-    <t>Jessica Maring</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
-    <t>LOB</t>
-  </si>
-  <si>
     <t>Yarway Corporation</t>
   </si>
   <si>
@@ -254,6 +250,33 @@
   </si>
   <si>
     <t>Celsius Network</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Opportunities</t>
+  </si>
+  <si>
+    <t>Engagements</t>
+  </si>
+  <si>
+    <t>System Admin</t>
+  </si>
+  <si>
+    <t>William Peluchiwski</t>
+  </si>
+  <si>
+    <t>Liz Hedgcock</t>
+  </si>
+  <si>
+    <t>Indrajeet Singh</t>
   </si>
 </sst>
 </file>
@@ -642,7 +665,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -653,6 +676,12 @@
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1188,7 +1217,7 @@
         <v>38</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AC2" t="s">
         <v>59</v>
@@ -1210,34 +1239,80 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A623B104-31C6-42A8-AE98-57FDC2862A9F}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E1B0EF-A5E2-4F8E-85E1-C720437C78C1}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>68</v>
+      <c r="C1" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
+      <c r="A2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1317,7 +1392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1329,19 +1404,19 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" s="6"/>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -1351,7 +1426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9566F5-BF1D-4424-961C-A03D3831C98B}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1361,17 +1436,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
